--- a/data/1.abstracting/26_06_01_deduplicated_processed.xlsx
+++ b/data/1.abstracting/26_06_01_deduplicated_processed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/1.abstracting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{96AA533F-C0D4-429F-983C-E0168CF2BA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C5A39DF-6198-46DE-B236-18408084554F}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{96AA533F-C0D4-429F-983C-E0168CF2BA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29A9ACAD-613B-43AF-A89F-7509BB71DFC0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EF905DA1-9734-4B13-93C6-8345AB56CF80}"/>
   </bookViews>
@@ -1091,9 +1091,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1131,7 +1131,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1237,7 +1237,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1379,7 +1379,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
